--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N18_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.79232697132364</v>
+        <v>3.053753132840091</v>
       </c>
       <c r="D2" t="n">
-        <v>19.35459528668511</v>
+        <v>3.145121734086331</v>
       </c>
       <c r="E2" t="n">
-        <v>22.90811510036879</v>
+        <v>3.722568703809928</v>
       </c>
       <c r="F2" t="n">
-        <v>12.40949996693498</v>
+        <v>2.016543744626934</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.53824313378849</v>
+        <v>2.52496450924063</v>
       </c>
       <c r="D3" t="n">
-        <v>14.17608246974877</v>
+        <v>2.303613401334175</v>
       </c>
       <c r="E3" t="n">
-        <v>22.90811510036879</v>
+        <v>3.722568703809928</v>
       </c>
       <c r="F3" t="n">
-        <v>12.40949996693498</v>
+        <v>2.016543744626934</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>84.53767122354846</v>
+        <v>13.73737157382662</v>
       </c>
       <c r="D4" t="n">
-        <v>2.207952944316054</v>
+        <v>0.3587923534513588</v>
       </c>
       <c r="E4" t="n">
-        <v>22.90811510036879</v>
+        <v>3.722568703809928</v>
       </c>
       <c r="F4" t="n">
-        <v>12.40949996693498</v>
+        <v>2.016543744626934</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.5166712983182</v>
+        <v>3.983959085976708</v>
       </c>
       <c r="D5" t="n">
-        <v>23.3277204179734</v>
+        <v>3.790754567920677</v>
       </c>
       <c r="E5" t="n">
-        <v>22.90811510036879</v>
+        <v>3.722568703809928</v>
       </c>
       <c r="F5" t="n">
-        <v>12.40949996693498</v>
+        <v>2.016543744626934</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.32314206214139</v>
+        <v>6.715010585097977</v>
       </c>
       <c r="D6" t="n">
-        <v>6.311156170757116</v>
+        <v>1.025562877748031</v>
       </c>
       <c r="E6" t="n">
-        <v>22.90811510036879</v>
+        <v>3.722568703809928</v>
       </c>
       <c r="F6" t="n">
-        <v>12.40949996693498</v>
+        <v>2.016543744626934</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>45.38493480742444</v>
+        <v>7.375051906206473</v>
       </c>
       <c r="D7" t="n">
-        <v>4.935353076442809</v>
+        <v>0.8019948749219564</v>
       </c>
       <c r="E7" t="n">
-        <v>22.90811510036879</v>
+        <v>3.722568703809928</v>
       </c>
       <c r="F7" t="n">
-        <v>12.40949996693498</v>
+        <v>2.016543744626934</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>43.09274906958098</v>
+        <v>7.00257172380691</v>
       </c>
       <c r="D8" t="n">
-        <v>42.47377736249059</v>
+        <v>6.90198882140472</v>
       </c>
       <c r="E8" t="n">
-        <v>22.90811510036879</v>
+        <v>3.722568703809928</v>
       </c>
       <c r="F8" t="n">
-        <v>12.40949996693498</v>
+        <v>2.016543744626934</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>7.078478807075877</v>
+        <v>1.15025280614983</v>
       </c>
       <c r="D9" t="n">
-        <v>8.08407773173664</v>
+        <v>1.313662631407204</v>
       </c>
       <c r="E9" t="n">
-        <v>22.90811510036879</v>
+        <v>3.722568703809928</v>
       </c>
       <c r="F9" t="n">
-        <v>12.40949996693498</v>
+        <v>2.016543744626934</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
